--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>107952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411160.6354589771</v>
+        <v>411161</v>
       </c>
       <c r="R2" t="n">
-        <v>6199122.369508408</v>
+        <v>6199122</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2002-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>95737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411160.6354589771</v>
+        <v>411161</v>
       </c>
       <c r="R3" t="n">
-        <v>6199122.369508408</v>
+        <v>6199122</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>2002-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -915,7 +885,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Lund-Botaniska/Zoologiska museet</t>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110433</v>
+        <v>110446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97687</v>
+        <v>97689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110446</v>
+        <v>110455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110455</v>
+        <v>110460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97689</v>
+        <v>97690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110460</v>
+        <v>110488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97690</v>
+        <v>97717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110488</v>
+        <v>110494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97717</v>
+        <v>97723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110494</v>
+        <v>110501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97723</v>
+        <v>97730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110501</v>
+        <v>110505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97730</v>
+        <v>97734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110505</v>
+        <v>110513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97734</v>
+        <v>97741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110516</v>
+        <v>110521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97744</v>
+        <v>97749</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110521</v>
+        <v>110529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97749</v>
+        <v>97757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63544824</v>
       </c>
       <c r="B2" t="n">
-        <v>110529</v>
+        <v>110539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63544823</v>
       </c>
       <c r="B3" t="n">
-        <v>97757</v>
+        <v>97767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63544824</v>
+        <v>81439967</v>
       </c>
       <c r="B2" t="n">
-        <v>110539</v>
+        <v>103403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
+        <v>223246</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>500m SO Fogdarödshemmet, Sk</t>
+          <t>400 m SO Fogdarödshemmet, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411161</v>
+        <v>410959</v>
       </c>
       <c r="R2" t="n">
-        <v>6199122</v>
+        <v>6199220</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-08-16</t>
+          <t>2010-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-08-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Valeriana dioica/3D0c2308/Höör s:n/TTy/ /Torbjörn Tyler,Höör</t>
+          <t>2010-07-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,12 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>björksumpskog</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    731447</t>
+          <t>Längs skogsbilväg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -784,248 +774,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>63544823</v>
-      </c>
-      <c r="B3" t="n">
-        <v>97767</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>569</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granbräken</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Dryopteris cristata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>500m SO Fogdarödshemmet, Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>411161</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6199122</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Höör</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Höör</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2002-08-16</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2002-08-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Dryopteris cristata/3D0c2308/Höör s:n/TTy/ /Torbjörn Tyler,Höör</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>björksumpskog</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    731446</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Stefan Andersson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Torbjörn Tyler</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>81439967</v>
-      </c>
-      <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>223246</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>400 m SO Fogdarödshemmet, Sk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>410959.4020079517</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6199220.076034917</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Höör</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Höör</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2010-07-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2010-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Längs skogsbilväg</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Stefan Andersson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Torbjörn Tyler</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
         </is>

--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,8 +783,16 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81439967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>